--- a/marketing_report/outputs/Cursos/Otros_Reportes/reporte_journey_tiempos.xlsx
+++ b/marketing_report/outputs/Cursos/Otros_Reportes/reporte_journey_tiempos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="79">
   <si>
     <t>Persona_ID</t>
   </si>
@@ -88,9 +88,6 @@
     <t>EMAIL_antonellacarlamartinez2001@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_azullonghi@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_belenlpf015@gmail.com</t>
   </si>
   <si>
@@ -100,30 +97,24 @@
     <t>EMAIL_fgimenez@ucasal.edu.ar</t>
   </si>
   <si>
-    <t>EMAIL_giselagarrone03@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_gmlun2@gmail.com</t>
   </si>
   <si>
     <t>EMAIL_marihenderson@hotmail.com.ar</t>
   </si>
   <si>
+    <t>EMAIL_melilagoria@gmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_morab7080@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_roxanaojeda_berisso@hotmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_tamiiii495@gmail.com</t>
   </si>
   <si>
     <t>EMAIL_veles.elisa18@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_verorescobar@hotmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_victoriadohrman@gmail.com</t>
   </si>
   <si>
@@ -163,9 +154,6 @@
     <t>Antonella Martinez</t>
   </si>
   <si>
-    <t>&amp;deg;Azul&amp;deg;</t>
-  </si>
-  <si>
     <t>Eliana Belen Lopez Famoso</t>
   </si>
   <si>
@@ -175,28 +163,22 @@
     <t>Francisco</t>
   </si>
   <si>
-    <t>Gisela Garrone</t>
-  </si>
-  <si>
     <t>Maxi Luna</t>
   </si>
   <si>
     <t>Mariela Mariela</t>
   </si>
   <si>
+    <t>Melina Lagoria</t>
+  </si>
+  <si>
     <t>Belu&amp;lowbar;Davalos</t>
   </si>
   <si>
-    <t>Roxana Ojeda</t>
-  </si>
-  <si>
     <t>Tamara Micaela</t>
   </si>
   <si>
     <t>Elisa Veles</t>
-  </si>
-  <si>
-    <t>Veronica Escobar</t>
   </si>
   <si>
     <t>Victoria</t>
@@ -630,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -676,7 +658,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C2">
         <v>10977449</v>
@@ -694,19 +676,19 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -714,7 +696,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C3">
         <v>34859579</v>
@@ -732,19 +714,19 @@
         <v>128</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -752,7 +734,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C4">
         <v>36130225</v>
@@ -770,19 +752,19 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="K4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="L4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -790,7 +772,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C5">
         <v>37301681</v>
@@ -808,19 +790,19 @@
         <v>382</v>
       </c>
       <c r="H5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="J5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -828,7 +810,7 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C6">
         <v>38850802</v>
@@ -846,19 +828,19 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" t="s">
         <v>62</v>
       </c>
-      <c r="I6" t="s">
-        <v>68</v>
-      </c>
       <c r="J6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="L6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -866,7 +848,7 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C7">
         <v>40992434</v>
@@ -881,19 +863,19 @@
         <v>46056</v>
       </c>
       <c r="H7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" t="s">
         <v>63</v>
       </c>
-      <c r="I7" t="s">
-        <v>69</v>
-      </c>
       <c r="J7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="K7" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L7" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -901,7 +883,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C8">
         <v>44016484</v>
@@ -919,19 +901,19 @@
         <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I8" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -939,7 +921,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C9">
         <v>44912612</v>
@@ -957,19 +939,19 @@
         <v>391</v>
       </c>
       <c r="H9" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J9" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -977,7 +959,7 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C10">
         <v>46323997</v>
@@ -995,19 +977,19 @@
         <v>173</v>
       </c>
       <c r="H10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I10" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="K10" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="L10" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1015,7 +997,7 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11">
         <v>47716777</v>
@@ -1033,19 +1015,19 @@
         <v>162</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I11" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="K11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="L11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1053,7 +1035,7 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C12">
         <v>48781380</v>
@@ -1071,19 +1053,19 @@
         <v>161</v>
       </c>
       <c r="H12" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J12" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="K12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1091,7 +1073,7 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1106,19 +1088,19 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I13" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J13" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K13" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L13" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1126,34 +1108,34 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" s="2">
-        <v>45973</v>
+        <v>45958</v>
       </c>
       <c r="F14" s="2">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="G14">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H14" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K14" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L14" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1161,34 +1143,34 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" s="2">
-        <v>45958</v>
+        <v>45987</v>
       </c>
       <c r="F15" s="2">
-        <v>46058</v>
+        <v>46067</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I15" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J15" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K15" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L15" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1196,34 +1178,34 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2">
-        <v>45987</v>
+        <v>46021</v>
       </c>
       <c r="F16" s="2">
-        <v>46067</v>
+        <v>46013</v>
       </c>
       <c r="G16">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I16" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J16" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="K16" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L16" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1231,34 +1213,31 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2">
-        <v>46021</v>
+        <v>46072</v>
       </c>
       <c r="F17" s="2">
-        <v>46013</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
+        <v>46064</v>
       </c>
       <c r="H17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I17" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="J17" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="K17" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="L17" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1266,34 +1245,31 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" s="2">
-        <v>46025</v>
+        <v>45739</v>
       </c>
       <c r="F18" s="2">
-        <v>46057</v>
-      </c>
-      <c r="G18">
-        <v>32</v>
+        <v>46064</v>
       </c>
       <c r="H18" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1301,31 +1277,31 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" s="2">
-        <v>46072</v>
+        <v>46030</v>
       </c>
       <c r="F19" s="2">
-        <v>46064</v>
+        <v>46057</v>
       </c>
       <c r="H19" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I19" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J19" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K19" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L19" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1333,31 +1309,34 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2">
-        <v>45739</v>
+        <v>45904</v>
       </c>
       <c r="F20" s="2">
-        <v>46064</v>
+        <v>46056</v>
+      </c>
+      <c r="G20">
+        <v>152</v>
       </c>
       <c r="H20" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I20" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J20" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K20" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="L20" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1365,34 +1344,31 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E21" s="2">
-        <v>45904</v>
+        <v>46009</v>
       </c>
       <c r="F21" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G21">
-        <v>152</v>
+        <v>46064</v>
       </c>
       <c r="H21" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I21" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J21" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K21" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="L21" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1400,34 +1376,34 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22" s="2">
-        <v>46079</v>
+        <v>45983</v>
       </c>
       <c r="F22" s="2">
-        <v>46057</v>
+        <v>46019</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I22" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J22" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K22" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L22" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1435,136 +1411,34 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2">
-        <v>46009</v>
+        <v>45901</v>
       </c>
       <c r="F23" s="2">
-        <v>46064</v>
+        <v>46055</v>
+      </c>
+      <c r="G23">
+        <v>154</v>
       </c>
       <c r="H23" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J23" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="K23" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="L23" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24" s="2">
-        <v>45983</v>
-      </c>
-      <c r="F24" s="2">
-        <v>46019</v>
-      </c>
-      <c r="G24">
-        <v>36</v>
-      </c>
-      <c r="H24" t="s">
-        <v>62</v>
-      </c>
-      <c r="I24" t="s">
-        <v>78</v>
-      </c>
-      <c r="J24" t="s">
-        <v>78</v>
-      </c>
-      <c r="K24" t="s">
-        <v>83</v>
-      </c>
-      <c r="L24" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25" s="2">
-        <v>45963</v>
-      </c>
-      <c r="F25" s="2">
-        <v>46057</v>
-      </c>
-      <c r="G25">
-        <v>94</v>
-      </c>
-      <c r="H25" t="s">
-        <v>62</v>
-      </c>
-      <c r="I25" t="s">
-        <v>65</v>
-      </c>
-      <c r="J25" t="s">
-        <v>65</v>
-      </c>
-      <c r="K25" t="s">
-        <v>83</v>
-      </c>
-      <c r="L25" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-      <c r="E26" s="2">
-        <v>45901</v>
-      </c>
-      <c r="F26" s="2">
-        <v>46055</v>
-      </c>
-      <c r="G26">
-        <v>154</v>
-      </c>
-      <c r="H26" t="s">
-        <v>62</v>
-      </c>
-      <c r="I26" t="s">
-        <v>79</v>
-      </c>
-      <c r="J26" t="s">
-        <v>70</v>
-      </c>
-      <c r="K26" t="s">
-        <v>70</v>
-      </c>
-      <c r="L26" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
